--- a/lucas/import_data/dataset_meta/excel/dataset.xlsx
+++ b/lucas/import_data/dataset_meta/excel/dataset.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -146,6 +146,72 @@
   </si>
   <si>
     <t xml:space="preserve">geographic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eu-eea biogeographical regions 2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">biogeo16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biogeographical regions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eu-eea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">info@eea.europa.eu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">biogeographic region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no profiling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no license</t>
+  </si>
+  <si>
+    <t xml:space="preserve">biogeography</t>
+  </si>
+  <si>
+    <t xml:space="preserve">biogepgraphy, europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.eea.europa.eu/en/datahub/datahubitem-view/11db8d14-f167-4cd5-9205-95638dfd9618</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">The 2016 version 1 of the European Biogeographical Regions dataset maintained by the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">European Environment Agency (EEA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -155,7 +221,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -176,6 +242,18 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -220,7 +298,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -231,6 +309,14 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -253,37 +339,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -356,8 +442,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AB3"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.42"/>
@@ -517,7 +603,66 @@
         <v>41</v>
       </c>
     </row>
+    <row r="3" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>20160331</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>20261231</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O3" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB3" s="0" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="Q3" r:id="rId1" display="European Environment Agency (EEA"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/lucas/import_data/dataset_meta/excel/dataset.xlsx
+++ b/lucas/import_data/dataset_meta/excel/dataset.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -28,6 +28,9 @@
     <t xml:space="preserve">alias</t>
   </si>
   <si>
+    <t xml:space="preserve">tag</t>
+  </si>
+  <si>
     <t xml:space="preserve">display_name</t>
   </si>
   <si>
@@ -127,7 +130,7 @@
     <t xml:space="preserve">soil</t>
   </si>
   <si>
-    <t xml:space="preserve">depth_cm</t>
+    <t xml:space="preserve">depth cm</t>
   </si>
   <si>
     <t xml:space="preserve">jrc-lucas</t>
@@ -154,7 +157,7 @@
     <t xml:space="preserve">biogeo16</t>
   </si>
   <si>
-    <t xml:space="preserve">Biogeographical regions</t>
+    <t xml:space="preserve">Biogeographical regions EU 2016</t>
   </si>
   <si>
     <t xml:space="preserve">eu-eea</t>
@@ -184,34 +187,7 @@
     <t xml:space="preserve">https://www.eea.europa.eu/en/datahub/datahubitem-view/11db8d14-f167-4cd5-9205-95638dfd9618</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">The 2016 version 1 of the European Biogeographical Regions dataset maintained by the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">European Environment Agency (EEA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">The 2016 version 1 of the European Biogeographical Regions dataset maintained by the European Environment Agency (EEA)</t>
   </si>
 </sst>
 </file>
@@ -221,7 +197,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -242,11 +218,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -298,7 +269,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -312,10 +283,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -442,23 +409,24 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB3"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="36.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="1" width="24.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="33.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="36.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="16.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="15.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="15.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="20.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="20.93"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="36.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="36.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="24.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="21.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="33.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="36.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="16.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="15.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="15.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="20.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="20.93"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="36.05"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -546,69 +514,75 @@
       <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="2" t="n">
         <v>20090101</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="I2" s="2" t="n">
         <v>20221231</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>36</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="O2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="U2" s="1" t="n">
+      <c r="R2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="V2" s="1" t="n">
         <v>1</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="AB2" s="1" t="s">
         <v>41</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>44</v>
@@ -619,22 +593,22 @@
       <c r="E3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="1" t="n">
         <v>20160331</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="I3" s="1" t="n">
         <v>20261231</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J3" s="0" t="s">
+      <c r="J3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="0" t="s">
+      <c r="K3" s="1" t="s">
         <v>50</v>
       </c>
       <c r="M3" s="1" t="s">
@@ -643,25 +617,28 @@
       <c r="N3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="O3" s="0" t="s">
+      <c r="O3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="P3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="Z3" s="1" t="n">
+      <c r="R3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AA3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB3" s="0" t="s">
+      <c r="AB3" s="1" t="s">
         <v>41</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="Q3" r:id="rId1" display="European Environment Agency (EEA"/>
+    <hyperlink ref="R3" r:id="rId1" display="The 2016 version 1 of the European Biogeographical Regions dataset maintained by the European Environment Agency (EEA)"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
